--- a/Gym Track.xlsx
+++ b/Gym Track.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xkyh0\Gym-Track\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E396DE-A2BA-4A86-AE5D-E8FCBD6CDBF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5B6D93-C400-4B58-BB4C-3ECDABD4494C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -512,7 +512,7 @@
     <t>Total Session:</t>
   </si>
   <si>
-    <t>Testt</t>
+    <t>Testing</t>
   </si>
 </sst>
 </file>
@@ -8677,14 +8677,14 @@
         <f>COUNTIFS(Control!$L$3:$L$1464,"&gt;="&amp;Control!$A$35,Control!$L$3:$L$1464,"&lt;"&amp;EDATE(Control!$A$35,1),Control!$N$3:$N$1464,"Gym")</f>
         <v>0</v>
       </c>
-      <c r="K6" s="49" t="s">
-        <v>145</v>
-      </c>
       <c r="N6" s="49" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K7" s="49" t="s">
+        <v>145</v>
+      </c>
       <c r="N7" s="49" t="s">
         <v>126</v>
       </c>
@@ -32984,7 +32984,7 @@
         <v>47432</v>
       </c>
       <c r="C1442" s="55" t="str">
-        <f t="shared" ref="C1442:C1505" si="22">TEXT(B1442,"ddd")</f>
+        <f t="shared" ref="C1442:C1493" si="22">TEXT(B1442,"ddd")</f>
         <v>Sat</v>
       </c>
       <c r="D1442" s="55"/>
